--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T1_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T1_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.286</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>0.473</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>0.231</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
-  </si>
-  <si>
-    <t>0.769</t>
-  </si>
-  <si>
-    <t>(0.219)</t>
-  </si>
-  <si>
-    <t>1.165</t>
-  </si>
-  <si>
-    <t>(0.195)</t>
-  </si>
-  <si>
-    <t>0.319</t>
-  </si>
-  <si>
-    <t>(0.076)</t>
+    <t>0.299</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>0.494</t>
+  </si>
+  <si>
+    <t>(0.054)</t>
+  </si>
+  <si>
+    <t>0.241</t>
+  </si>
+  <si>
+    <t>(0.046)</t>
+  </si>
+  <si>
+    <t>0.805</t>
+  </si>
+  <si>
+    <t>(0.228)</t>
+  </si>
+  <si>
+    <t>1.218</t>
+  </si>
+  <si>
+    <t>(0.202)</t>
+  </si>
+  <si>
+    <t>0.333</t>
+  </si>
+  <si>
+    <t>(0.080)</t>
   </si>
   <si>
     <t>23</t>
@@ -138,7 +138,7 @@
     <t>(0.166)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.193*</t>
-  </si>
-  <si>
-    <t>0.354***</t>
-  </si>
-  <si>
-    <t>0.508***</t>
-  </si>
-  <si>
-    <t>1.144</t>
-  </si>
-  <si>
-    <t>2.096***</t>
-  </si>
-  <si>
-    <t>0.681***</t>
+    <t>0.179</t>
+  </si>
+  <si>
+    <t>0.332***</t>
+  </si>
+  <si>
+    <t>0.498***</t>
+  </si>
+  <si>
+    <t>1.108</t>
+  </si>
+  <si>
+    <t>2.042***</t>
+  </si>
+  <si>
+    <t>0.667***</t>
   </si>
 </sst>
 </file>
